--- a/report-2026-06-22.xlsx
+++ b/report-2026-06-22.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="1443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1445">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-22T22:42:58+05:30</t>
+    <t>Generated 2026-06-22T22:48:12+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-22T22:40:57+05:30 (2m0s ago)</t>
+    <t>2026-06-22T22:46:12+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4339,10 +4339,16 @@
     <t>22:40:57.997</t>
   </si>
   <si>
+    <t>2026-06-22T22:45:59.8444842+05:30</t>
+  </si>
+  <si>
+    <t>22:45:59.844</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-22T22:42:58+05:30</t>
+    <t>2026-06-22T22:48:12+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4937,7 +4943,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 18s</t>
+          <t>0h 7m 32s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4957,7 +4963,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 21m 3s</t>
+          <t>25h 22m 5s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4967,7 +4973,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:42:58</t>
+          <t>22:48:12</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5080,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:42:58</t>
+          <t>22:48:12</t>
         </is>
       </c>
     </row>
@@ -5188,12 +5194,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>[stale-takeover]</t>
+          <t>[renewed]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:40:57.9979938+05:30</t>
+          <t>2026-06-22T22:45:59.8444842+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5203,12 +5209,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:40:57.997</t>
+          <t>22:45:59.844</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>stale-takeover</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5236,7 +5242,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>stale-takeover</t>
+          <t>renewed</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -41580,18 +41586,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="711">
-      <c r="A711" t="s">
+    <row r="710">
+      <c r="A710" s="4">
+        <v>693</v>
+      </c>
+      <c r="B710" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="B711" t="s">
+      <c r="C710" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D710" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="D711" t="s">
+      <c r="E710" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F710" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G710" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H710" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I710" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J710" s="4">
+        <v>0</v>
+      </c>
+      <c r="K710" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L710" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="s">
         <v>1442</v>
       </c>
-      <c r="E711">
-        <v>692</v>
+      <c r="B712" t="s">
+        <v>1443</v>
+      </c>
+      <c r="D712" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E712">
+        <v>693</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-22.xlsx
+++ b/report-2026-06-22.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1445" uniqueCount="1445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1447">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-22T22:48:12+05:30</t>
+    <t>Generated 2026-06-22T22:53:13+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-22T22:46:12+05:30 (2m0s ago)</t>
+    <t>2026-06-22T22:51:13+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4345,10 +4345,16 @@
     <t>22:45:59.844</t>
   </si>
   <si>
+    <t>2026-06-22T22:50:59.9398109+05:30</t>
+  </si>
+  <si>
+    <t>22:50:59.939</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-22T22:48:12+05:30</t>
+    <t>2026-06-22T22:53:13+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4943,7 +4949,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 32s</t>
+          <t>0h 12m 33s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4963,7 +4969,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 22m 5s</t>
+          <t>25h 24m 45s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4973,7 +4979,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:48:12</t>
+          <t>22:53:13</t>
         </is>
       </c>
     </row>
@@ -5005,72 +5011,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>amd64</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.0.64</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>websocket</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>157835.5</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10.0.64</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>disconnected</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Jun 17 10:41 PM</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0h 3m 12s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5080,7 +5086,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:48:12</t>
+          <t>22:53:13</t>
         </is>
       </c>
     </row>
@@ -5199,7 +5205,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:45:59.8444842+05:30</t>
+          <t>2026-06-22T22:50:59.9398109+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5209,7 +5215,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:45:59.844</t>
+          <t>22:50:59.939</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41624,18 +41630,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="712">
-      <c r="A712" t="s">
+    <row r="711">
+      <c r="A711" s="4">
+        <v>694</v>
+      </c>
+      <c r="B711" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="B712" t="s">
+      <c r="C711" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D711" s="4" t="s">
         <v>1443</v>
       </c>
-      <c r="D712" t="s">
+      <c r="E711" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F711" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G711" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H711" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I711" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J711" s="4">
+        <v>0</v>
+      </c>
+      <c r="K711" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L711" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="s">
         <v>1444</v>
       </c>
-      <c r="E712">
-        <v>693</v>
+      <c r="B713" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D713" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E713">
+        <v>694</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-06-22.xlsx
+++ b/report-2026-06-22.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1447" uniqueCount="1447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="1449">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-06-22T22:53:13+05:30</t>
+    <t>Generated 2026-06-22T22:58:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-06-22T22:51:13+05:30 (2m0s ago)</t>
+    <t>2026-06-22T22:56:17+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -4351,10 +4351,16 @@
     <t>22:50:59.939</t>
   </si>
   <si>
+    <t>2026-06-22T22:56:17.1194114+05:30</t>
+  </si>
+  <si>
+    <t>22:56:17.119</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-06-22T22:53:13+05:30</t>
+    <t>2026-06-22T22:58:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -4949,7 +4955,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 33s</t>
+          <t>0h 17m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -4969,7 +4975,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>25h 24m 45s</t>
+          <t>25h 26m 33s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -4979,7 +4985,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>22:53:13</t>
+          <t>22:58:17</t>
         </is>
       </c>
     </row>
@@ -5011,7 +5017,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5021,42 +5027,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>websocket</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>157835.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -5066,7 +5072,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jun 17 10:41 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -5076,7 +5082,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0h 3m 12s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -5086,7 +5092,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>22:53:13</t>
+          <t>22:58:17</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-22T22:50:59.9398109+05:30</t>
+          <t>2026-06-22T22:56:17.1194114+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5215,7 +5221,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22:50:59.939</t>
+          <t>22:56:17.119</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -41668,18 +41674,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="713">
-      <c r="A713" t="s">
+    <row r="712">
+      <c r="A712" s="4">
+        <v>695</v>
+      </c>
+      <c r="B712" s="4" t="s">
         <v>1444</v>
       </c>
-      <c r="B713" t="s">
+      <c r="C712" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="D712" s="4" t="s">
         <v>1445</v>
       </c>
-      <c r="D713" t="s">
+      <c r="E712" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F712" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G712" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H712" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I712" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J712" s="4">
+        <v>0</v>
+      </c>
+      <c r="K712" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="L712" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="s">
         <v>1446</v>
       </c>
-      <c r="E713">
-        <v>694</v>
+      <c r="B714" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D714" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E714">
+        <v>695</v>
       </c>
     </row>
   </sheetData>
